--- a/Execution_Summary.xlsx
+++ b/Execution_Summary.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27 15:53:56</t>
+          <t>2026-08-27 16:46:34</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>

--- a/Execution_Summary.xlsx
+++ b/Execution_Summary.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27 16:46:34</t>
+          <t>2026-08-27 17:28:36</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
